--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104501_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104501_W5.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.164</v>
+        <v>3.765</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2504</v>
+        <v>0.2154</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4144</v>
+        <v>3.5496</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.0998</v>
+        <v>-2.1317</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6671</v>
+        <v>0.6391</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.7669</v>
+        <v>-2.7709</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.4817</v>
+        <v>-2.5377</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7784</v>
+        <v>0.7402</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.2601</v>
+        <v>-3.2779</v>
       </c>
       <c r="M2" t="n">
-        <v>0.382</v>
+        <v>0.406</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6875</v>
+        <v>-0.0523</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.234</v>
+        <v>-0.6926</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5465</v>
+        <v>0.6404</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6829</v>
+        <v>3.6727</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1458</v>
+        <v>4.1287</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4628</v>
+        <v>-0.456</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3446</v>
+        <v>0.6312</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5505</v>
+        <v>0.8154</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.206</v>
+        <v>-0.1842</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2018</v>
+        <v>-0.2029</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.551</v>
+        <v>-0.5623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3493</v>
+        <v>0.3594</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5062</v>
+        <v>0.4834</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3943</v>
+        <v>0.3717</v>
       </c>
       <c r="L3" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.708</v>
+        <v>-0.6863</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6805</v>
+        <v>-0.0278</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0858</v>
+        <v>0.3807</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4053</v>
+        <v>-0.4085</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6642</v>
+        <v>0.5502</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4878</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1764</v>
+        <v>-0.0047</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1452</v>
+        <v>0.1483</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5397</v>
+        <v>0.5399</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6088</v>
+        <v>0.6061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4636</v>
+        <v>-0.4578</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2922</v>
+        <v>0.1743</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>-0.0512</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4131</v>
+        <v>0.2254</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1459</v>
+        <v>0.1096</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0144</v>
+        <v>-0.7927</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1314</v>
+        <v>0.9023</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1153</v>
+        <v>-0.5138</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.775</v>
+        <v>-1.2406</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8903</v>
+        <v>0.7268</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1855</v>
+        <v>0.7317</v>
       </c>
       <c r="K5" t="n">
-        <v>0.218</v>
+        <v>-0.5935</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9675</v>
+        <v>1.3252</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0702</v>
+        <v>-1.2455</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.993</v>
+        <v>-0.6471</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>-0.5984</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1893</v>
+        <v>-0.6725</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3902</v>
+        <v>-0.544</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2008</v>
+        <v>-0.1286</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.3874</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.463</v>
+        <v>-0.3642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8405</v>
+        <v>-0.0232</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5077</v>
+        <v>0.1251</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.238</v>
+        <v>-0.7673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.8924</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7625</v>
+        <v>1.1706</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5754</v>
+        <v>0.2101</v>
       </c>
       <c r="L6" t="n">
-        <v>1.338</v>
+        <v>0.9605</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2702</v>
+        <v>-1.0455</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6626</v>
+        <v>-0.9774</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6077</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4097</v>
+        <v>-0.3531</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2521</v>
+        <v>0.039</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1576</v>
+        <v>-0.3921</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.4529</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1501</v>
+        <v>-1.6309</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8301</v>
+        <v>1.1779</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1685</v>
+        <v>-1.202</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0433</v>
+        <v>-0.1491</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1253</v>
+        <v>-1.0529</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0212</v>
+        <v>0.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.091</v>
+        <v>0.9718</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9302</v>
+        <v>-0.8718</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8526</v>
+        <v>-1.302</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0477</v>
+        <v>-1.1209</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.805</v>
+        <v>-0.1811</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>-1.072</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1905</v>
+        <v>-0.5927</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1905</v>
+        <v>-0.4793</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3948</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.6087</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.525</v>
+        <v>1.2054</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7967</v>
+        <v>-1.8141</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2798</v>
+        <v>1.1646</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6694</v>
+        <v>1.0426</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4271</v>
+        <v>2.0092</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4644</v>
+        <v>1.0859</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.9233</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8526</v>
+        <v>-0.8446</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.205</v>
+        <v>-0.0433</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.8012</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2392</v>
+        <v>0.0697</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.1209</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6566</v>
+        <v>0.1906</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1414</v>
+        <v>-1.3877</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1414</v>
+        <v>-1.3877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.265</v>
+        <v>-1.0068</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1902</v>
+        <v>-1.1369</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9252</v>
+        <v>0.1301</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2024</v>
+        <v>0.8353</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1442</v>
+        <v>0.9676</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0582</v>
+        <v>-0.1323</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1265</v>
+        <v>-0.0285</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9902</v>
+        <v>0.7239</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8637</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3289</v>
+        <v>0.8638</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1344</v>
+        <v>0.2437</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1945</v>
+        <v>0.6201</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9488</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8773</v>
+        <v>-0.186</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1825</v>
+        <v>-0.4255</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6947</v>
+        <v>0.2396</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-3.0219</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.0219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4248</v>
+        <v>-1.0743</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0803</v>
+        <v>-1.54</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3446</v>
+        <v>0.4657</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8238</v>
+        <v>-1.2835</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9624</v>
+        <v>-0.6774</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1386</v>
+        <v>-0.6061</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0217</v>
+        <v>-0.4389</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7272999999999999</v>
+        <v>-0.4761</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.749</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8455</v>
+        <v>-0.8446</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2351</v>
+        <v>-0.2012</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6105</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5758</v>
+        <v>-0.1057</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.378</v>
+        <v>-0.4182</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1978</v>
+        <v>0.3126</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.0338</v>
+        <v>-0.1405</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0338</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7299</v>
+        <v>-2.2187</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.715</v>
+        <v>-4.6155</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9851</v>
+        <v>2.3968</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4924</v>
+        <v>0.3175</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9754</v>
+        <v>-1.1218</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.517</v>
+        <v>1.4393</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4145</v>
+        <v>-0.4609</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7774</v>
+        <v>-0.8628</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6371</v>
+        <v>0.4019</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0779</v>
+        <v>0.7784</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.198</v>
+        <v>-0.259</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1201</v>
+        <v>1.0374</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-4.0974</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2427</v>
+        <v>-0.4169</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9678</v>
+        <v>-0.602</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2749</v>
+        <v>0.1851</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.2983</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8436</v>
+        <v>-2.9389</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9862</v>
+        <v>-4.6866</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1426</v>
+        <v>1.7477</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3308</v>
+        <v>-3.4814</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1006</v>
+        <v>-2.9755</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4315</v>
+        <v>-0.506</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4243</v>
+        <v>-2.4376</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8321</v>
+        <v>-1.7969</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4078</v>
+        <v>-0.6407</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7551</v>
+        <v>-1.0439</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2685</v>
+        <v>-1.1786</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0237</v>
+        <v>0.1347</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.083</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0576</v>
+        <v>0.0174</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0253</v>
+        <v>0.0273</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0324</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3021</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8485</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.975299999999999</v>
+        <v>-3.6317</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.0073</v>
+        <v>-11.9757</v>
       </c>
       <c r="F13" t="n">
-        <v>8.031600000000001</v>
+        <v>8.3439</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.2003</v>
+        <v>-6.2245</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.2411</v>
+        <v>-4.304799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9589</v>
+        <v>-1.9199</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5586000000000005</v>
+        <v>-0.8026</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1214</v>
+        <v>0.9430999999999989</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6798</v>
+        <v>-1.7458</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.6414</v>
+        <v>-5.422</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.3625</v>
+        <v>-5.247800000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2791000000000001</v>
+        <v>-0.174</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6708</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.7962</v>
       </c>
       <c r="R13" t="n">
-        <v>20.4148</v>
+        <v>20.4867</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.964</v>
+        <v>-2.6249</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.357000000000001</v>
+        <v>-3.0001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.393</v>
+        <v>0.3753</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4820999999999999</v>
+        <v>-0.4731999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6526</v>
+        <v>6.6232</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1347</v>
+        <v>-7.096400000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.343</v>
+        <v>4.8844</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6785</v>
+        <v>1.7782</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6646</v>
+        <v>3.1062</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3881</v>
+        <v>4.402</v>
       </c>
       <c r="H14" t="n">
-        <v>1.512</v>
+        <v>1.5271</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8761</v>
+        <v>2.8749</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5234</v>
+        <v>3.509</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="L14" t="n">
-        <v>2.796</v>
+        <v>2.7851</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8647</v>
+        <v>0.893</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7847</v>
+        <v>0.8032</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3425</v>
+        <v>0.8678</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2571</v>
+        <v>-0.1375</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5996</v>
+        <v>1.0052</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9801</v>
+        <v>2.7025</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2089</v>
+        <v>2.8984</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2288</v>
+        <v>-0.196</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6736</v>
+        <v>1.6816</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0344</v>
+        <v>0.0508</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1975</v>
+        <v>2.1823</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2251</v>
+        <v>0.2241</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9724</v>
+        <v>1.9582</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2813</v>
+        <v>0.4275</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6956</v>
+        <v>0.0136</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4143</v>
+        <v>0.4138</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8967</v>
+        <v>2.2284</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2263</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6704</v>
+        <v>2.1327</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0949</v>
+        <v>1.1008</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0752</v>
+        <v>-0.0638</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1701</v>
+        <v>1.1646</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8675</v>
+        <v>0.8556</v>
       </c>
       <c r="K16" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2274</v>
+        <v>0.2452</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5592</v>
+        <v>-0.2382</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1875</v>
+        <v>-0.3046</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3717</v>
+        <v>0.0664</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4826</v>
+        <v>1.5392</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6404</v>
+        <v>-0.2771</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8421999999999999</v>
+        <v>1.8162</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4429</v>
+        <v>0.3037</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1283</v>
+        <v>-0.034</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3145</v>
+        <v>0.3378</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0346</v>
+        <v>-0.7167</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>-0.6937</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4082</v>
+        <v>1.0204</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.6597</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3145</v>
+        <v>0.3608</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0812</v>
+        <v>0.0871</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6472</v>
+        <v>-0.4324</v>
       </c>
       <c r="U17" t="n">
-        <v>0.434</v>
+        <v>0.5195</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>3.197</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>4.2865</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6065</v>
+        <v>0.856</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6775</v>
+        <v>0.1622</v>
       </c>
       <c r="F18" t="n">
-        <v>1.284</v>
+        <v>0.6937</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3206</v>
+        <v>0.4505</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0258</v>
+        <v>0.1346</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3464</v>
+        <v>0.3159</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6773</v>
+        <v>0.0345</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6691</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0081</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9979</v>
+        <v>0.416</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6433</v>
+        <v>0.1002</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3546</v>
+        <v>0.3159</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0415</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8865</v>
+        <v>0.4542</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9043</v>
+        <v>0.1765</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.2777</v>
       </c>
       <c r="V18" t="n">
-        <v>3.2138</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>4.3065</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5906</v>
+        <v>-0.0133</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0526</v>
+        <v>0.534</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4621</v>
+        <v>-0.5473</v>
       </c>
       <c r="G19" t="n">
-        <v>4.3727</v>
+        <v>4.371</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1674</v>
+        <v>4.1592</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2053</v>
+        <v>0.2118</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5979</v>
+        <v>4.5704</v>
       </c>
       <c r="K19" t="n">
-        <v>4.374</v>
+        <v>4.3469</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2252</v>
+        <v>-0.1993</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2066</v>
+        <v>-0.1877</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.9903</v>
+        <v>-5.0079</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2594</v>
+        <v>0.6644</v>
       </c>
       <c r="T19" t="n">
-        <v>0.738</v>
+        <v>0.2691</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5214</v>
+        <v>0.3953</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5526</v>
+        <v>-0.8419</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3483</v>
+        <v>-2.5981</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7958</v>
+        <v>1.7563</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4994</v>
+        <v>-2.4968</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2252</v>
+        <v>-1.2154</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2742</v>
+        <v>-1.2814</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4391</v>
+        <v>-2.4538</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0603</v>
+        <v>-0.043</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5858</v>
+        <v>0.2892</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4951</v>
+        <v>0.4335</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6764</v>
+        <v>-1.0348</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.874</v>
+        <v>-2.0697</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1976</v>
+        <v>1.0349</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0921</v>
+        <v>-2.6421</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7935</v>
+        <v>-0.8022</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2986</v>
+        <v>-1.8399</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2378</v>
+        <v>-1.8952</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.115</v>
+        <v>0.362</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1228</v>
+        <v>-2.2572</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.7469</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6785</v>
+        <v>-1.1642</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1759</v>
+        <v>0.4173</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5843</v>
+        <v>0.0139</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0484</v>
+        <v>-0.1745</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5359</v>
+        <v>0.1884</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7353</v>
+        <v>-1.0878</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6486</v>
+        <v>-1.6878</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9133</v>
+        <v>0.6001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6523</v>
+        <v>-1.1155</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8184</v>
+        <v>-0.8036</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8339</v>
+        <v>-0.3119</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8835</v>
+        <v>-0.2845</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3637</v>
+        <v>-0.1421</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2471</v>
+        <v>-0.1424</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7689</v>
+        <v>-0.831</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1821</v>
+        <v>-0.6615</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4132</v>
+        <v>-0.1695</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6708</v>
+        <v>0.0278</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>0.1901</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0944</v>
+        <v>-0.1623</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8623</v>
+        <v>-1.6847</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.509</v>
+        <v>-3.4737</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.789</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.675</v>
+        <v>0.8317</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9842</v>
+        <v>2.3289</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3092</v>
+        <v>-1.4971</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8547</v>
+        <v>0.4847</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9666</v>
+        <v>2.0717</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112</v>
+        <v>-1.587</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1797</v>
+        <v>0.347</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0176</v>
+        <v>0.2572</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1973</v>
+        <v>0.0898</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-5.0079</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5839</v>
+        <v>0.5111</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3852</v>
+        <v>-0.04</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1987</v>
+        <v>0.551</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8639</v>
+        <v>0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0975</v>
+        <v>-2.7779</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.781</v>
+        <v>-3.7059</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6835</v>
+        <v>0.928</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8262</v>
+        <v>-0.6624</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3216</v>
+        <v>-0.9769</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4954</v>
+        <v>0.3145</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5128</v>
+        <v>-0.8643</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0882</v>
+        <v>-0.976</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5754</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3134</v>
+        <v>0.2019</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2334</v>
+        <v>-0.0009</v>
       </c>
       <c r="O24" t="n">
-        <v>0.08</v>
+        <v>0.2028</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4025</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.9903</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0931</v>
+        <v>0.6584</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3962</v>
+        <v>0.2086</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4893</v>
+        <v>0.4498</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3856</v>
+        <v>-1.8634</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.9754</v>
+        <v>4.770099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.031700000000001</v>
+        <v>-8.3438</v>
       </c>
       <c r="F25" t="n">
-        <v>12.0072</v>
+        <v>13.1138</v>
       </c>
       <c r="G25" t="n">
-        <v>6.2002</v>
+        <v>6.224500000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2414</v>
+        <v>4.3047</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9587</v>
+        <v>1.92</v>
       </c>
       <c r="J25" t="n">
-        <v>5.641300000000001</v>
+        <v>5.422000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>5.362499999999999</v>
+        <v>5.2478</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2790999999999995</v>
+        <v>0.1739999999999991</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5586999999999999</v>
+        <v>0.8026000000000002</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1212</v>
+        <v>-0.9430999999999998</v>
       </c>
       <c r="O25" t="n">
-        <v>1.6798</v>
+        <v>1.7459</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.6708</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.4149</v>
+        <v>-20.4869</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9638</v>
+        <v>3.7632</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3932000000000001</v>
+        <v>-0.3754000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.357</v>
+        <v>4.1383</v>
       </c>
       <c r="V25" t="n">
-        <v>0.4822</v>
+        <v>0.4734000000000003</v>
       </c>
       <c r="W25" t="n">
-        <v>7.134899999999999</v>
+        <v>7.0966</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.652699999999999</v>
+        <v>-6.6232</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104501_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104501_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.456</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.3877</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.0219</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.843</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.096400000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104501_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.6232</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
